--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\WI\elec\MPCbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{610DBEE0-71D4-42B0-93B8-1EC1D32D7782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB724114-E04C-49AB-87E3-18B8CB2CEC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="195" windowWidth="20805" windowHeight="9765" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Population by state" sheetId="4" r:id="rId2"/>
-    <sheet name="solar PV" sheetId="5" r:id="rId3"/>
-    <sheet name="solar thermal" sheetId="6" r:id="rId4"/>
-    <sheet name="offshore wind" sheetId="7" r:id="rId5"/>
-    <sheet name="onshore wind" sheetId="8" r:id="rId6"/>
-    <sheet name="bio" sheetId="9" r:id="rId7"/>
-    <sheet name="geothermal" sheetId="10" r:id="rId8"/>
-    <sheet name="hydro" sheetId="11" r:id="rId9"/>
-    <sheet name="Data" sheetId="2" r:id="rId10"/>
-    <sheet name="MPCbS" sheetId="3" r:id="rId11"/>
+    <sheet name="coal ban" sheetId="12" r:id="rId2"/>
+    <sheet name="Population by state" sheetId="4" r:id="rId3"/>
+    <sheet name="solar PV" sheetId="5" r:id="rId4"/>
+    <sheet name="solar thermal" sheetId="6" r:id="rId5"/>
+    <sheet name="offshore wind" sheetId="7" r:id="rId6"/>
+    <sheet name="onshore wind" sheetId="8" r:id="rId7"/>
+    <sheet name="bio" sheetId="9" r:id="rId8"/>
+    <sheet name="geothermal" sheetId="10" r:id="rId9"/>
+    <sheet name="hydro" sheetId="11" r:id="rId10"/>
+    <sheet name="Data" sheetId="2" r:id="rId11"/>
+    <sheet name="MPCbS" sheetId="3" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="282">
   <si>
     <t>Source:</t>
   </si>
@@ -879,6 +880,15 @@
   </si>
   <si>
     <t>Great Lakes, Upper Mississippi</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>ban on new coal?</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1705,7 +1715,7 @@
         <v>196</v>
       </c>
       <c r="C1" s="24">
-        <v>45294</v>
+        <v>45301</v>
       </c>
       <c r="H1" s="25" t="s">
         <v>100</v>
@@ -2201,6 +2211,2866 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034993D7-C303-48FF-99F6-02F9737AB03C}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" style="28" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" style="28" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="8.7109375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="22.42578125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="28" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" style="28" customWidth="1"/>
+    <col min="8" max="8" width="23.5703125" style="28" customWidth="1"/>
+    <col min="9" max="9" width="23.85546875" style="28" customWidth="1"/>
+    <col min="10" max="10" width="22.28515625" style="28" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" style="28" customWidth="1"/>
+    <col min="12" max="26" width="8.7109375" style="28" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="str">
+        <f>About!B2</f>
+        <v>WI</v>
+      </c>
+      <c r="B1" s="32">
+        <f>SUMIFS(D5:D54,A5:A54,A1)</f>
+        <v>522.14611872146122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A2" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60"/>
+      <c r="F2" s="60"/>
+      <c r="I2" s="51"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="I3" s="32"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A4" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="E4" s="51"/>
+      <c r="F4" s="32">
+        <f>8760*0.5</f>
+        <v>4380</v>
+      </c>
+      <c r="G4" s="62" t="s">
+        <v>231</v>
+      </c>
+      <c r="I4" s="32"/>
+    </row>
+    <row r="5" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="32">
+        <v>4103</v>
+      </c>
+      <c r="C5" s="32">
+        <f t="shared" ref="C5:C54" si="0">B5/$F$4</f>
+        <v>0.93675799086757994</v>
+      </c>
+      <c r="D5" s="32">
+        <f t="shared" ref="D5:D54" si="1">C5*1000</f>
+        <v>936.75799086757991</v>
+      </c>
+      <c r="I5" s="32"/>
+    </row>
+    <row r="6" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="32">
+        <v>23676</v>
+      </c>
+      <c r="C6" s="32">
+        <f t="shared" si="0"/>
+        <v>5.4054794520547942</v>
+      </c>
+      <c r="D6" s="32">
+        <f t="shared" si="1"/>
+        <v>5405.4794520547939</v>
+      </c>
+      <c r="I6" s="32"/>
+    </row>
+    <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="B7" s="32">
+        <v>1303</v>
+      </c>
+      <c r="C7" s="32">
+        <f t="shared" si="0"/>
+        <v>0.29748858447488585</v>
+      </c>
+      <c r="D7" s="32">
+        <f t="shared" si="1"/>
+        <v>297.48858447488584</v>
+      </c>
+      <c r="I7" s="32"/>
+    </row>
+    <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="B8" s="32">
+        <v>6093</v>
+      </c>
+      <c r="C8" s="32">
+        <f t="shared" si="0"/>
+        <v>1.3910958904109589</v>
+      </c>
+      <c r="D8" s="32">
+        <f t="shared" si="1"/>
+        <v>1391.0958904109589</v>
+      </c>
+      <c r="I8" s="32"/>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="B9" s="32">
+        <v>30024</v>
+      </c>
+      <c r="C9" s="32">
+        <f t="shared" si="0"/>
+        <v>6.8547945205479452</v>
+      </c>
+      <c r="D9" s="32">
+        <f t="shared" si="1"/>
+        <v>6854.7945205479455</v>
+      </c>
+      <c r="I9" s="32"/>
+    </row>
+    <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="B10" s="32">
+        <v>7789</v>
+      </c>
+      <c r="C10" s="32">
+        <f t="shared" si="0"/>
+        <v>1.7783105022831049</v>
+      </c>
+      <c r="D10" s="32">
+        <f t="shared" si="1"/>
+        <v>1778.3105022831051</v>
+      </c>
+      <c r="I10" s="32"/>
+    </row>
+    <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="32">
+        <v>922</v>
+      </c>
+      <c r="C11" s="32">
+        <f t="shared" si="0"/>
+        <v>0.21050228310502284</v>
+      </c>
+      <c r="D11" s="32">
+        <f t="shared" si="1"/>
+        <v>210.50228310502283</v>
+      </c>
+      <c r="I11" s="32"/>
+    </row>
+    <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="32">
+        <v>31</v>
+      </c>
+      <c r="C12" s="32">
+        <f t="shared" si="0"/>
+        <v>7.0776255707762558E-3</v>
+      </c>
+      <c r="D12" s="32">
+        <f t="shared" si="1"/>
+        <v>7.0776255707762559</v>
+      </c>
+      <c r="I12" s="32"/>
+    </row>
+    <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="32">
+        <v>682</v>
+      </c>
+      <c r="C13" s="32">
+        <f t="shared" si="0"/>
+        <v>0.15570776255707763</v>
+      </c>
+      <c r="D13" s="32">
+        <f t="shared" si="1"/>
+        <v>155.70776255707764</v>
+      </c>
+      <c r="I13" s="32"/>
+    </row>
+    <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="32">
+        <v>1988</v>
+      </c>
+      <c r="C14" s="32">
+        <f t="shared" si="0"/>
+        <v>0.45388127853881277</v>
+      </c>
+      <c r="D14" s="32">
+        <f t="shared" si="1"/>
+        <v>453.88127853881275</v>
+      </c>
+      <c r="I14" s="32"/>
+    </row>
+    <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="32">
+        <v>2602</v>
+      </c>
+      <c r="C15" s="32">
+        <f t="shared" si="0"/>
+        <v>0.59406392694063925</v>
+      </c>
+      <c r="D15" s="32">
+        <f t="shared" si="1"/>
+        <v>594.06392694063925</v>
+      </c>
+      <c r="G15" s="32"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="32"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="32"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="32"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="32"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="32"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="32"/>
+    </row>
+    <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="32">
+        <v>18758</v>
+      </c>
+      <c r="C16" s="32">
+        <f t="shared" si="0"/>
+        <v>4.2826484018264841</v>
+      </c>
+      <c r="D16" s="32">
+        <f t="shared" si="1"/>
+        <v>4282.6484018264837</v>
+      </c>
+      <c r="G16" s="32"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="63"/>
+      <c r="K16" s="32"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="32"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
+    </row>
+    <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" s="32">
+        <v>4883</v>
+      </c>
+      <c r="C17" s="32">
+        <f t="shared" si="0"/>
+        <v>1.1148401826484018</v>
+      </c>
+      <c r="D17" s="32">
+        <f t="shared" si="1"/>
+        <v>1114.8401826484019</v>
+      </c>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+    </row>
+    <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="B18" s="63">
+        <v>2394</v>
+      </c>
+      <c r="C18" s="32">
+        <f t="shared" si="0"/>
+        <v>0.54657534246575346</v>
+      </c>
+      <c r="D18" s="32">
+        <f t="shared" si="1"/>
+        <v>546.57534246575347</v>
+      </c>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="32"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="32"/>
+    </row>
+    <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B19" s="32">
+        <v>2818</v>
+      </c>
+      <c r="C19" s="32">
+        <f t="shared" si="0"/>
+        <v>0.64337899543378996</v>
+      </c>
+      <c r="D19" s="32">
+        <f t="shared" si="1"/>
+        <v>643.37899543379001</v>
+      </c>
+      <c r="G19" s="32"/>
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="32"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="32"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
+    </row>
+    <row r="20" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="32">
+        <v>2508</v>
+      </c>
+      <c r="C20" s="32">
+        <f t="shared" si="0"/>
+        <v>0.57260273972602738</v>
+      </c>
+      <c r="D20" s="32">
+        <f t="shared" si="1"/>
+        <v>572.60273972602738</v>
+      </c>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" s="32">
+        <v>4255</v>
+      </c>
+      <c r="C21" s="32">
+        <f t="shared" si="0"/>
+        <v>0.97146118721461183</v>
+      </c>
+      <c r="D21" s="32">
+        <f t="shared" si="1"/>
+        <v>971.46118721461187</v>
+      </c>
+      <c r="I21" s="32"/>
+    </row>
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" s="32">
+        <v>2423</v>
+      </c>
+      <c r="C22" s="32">
+        <f t="shared" si="0"/>
+        <v>0.55319634703196352</v>
+      </c>
+      <c r="D22" s="32">
+        <f t="shared" si="1"/>
+        <v>553.19634703196357</v>
+      </c>
+      <c r="I22" s="32"/>
+    </row>
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" s="32">
+        <v>3916</v>
+      </c>
+      <c r="C23" s="32">
+        <f t="shared" si="0"/>
+        <v>0.8940639269406393</v>
+      </c>
+      <c r="D23" s="32">
+        <f t="shared" si="1"/>
+        <v>894.06392694063925</v>
+      </c>
+      <c r="I23" s="32"/>
+    </row>
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" s="32">
+        <v>814</v>
+      </c>
+      <c r="C24" s="32">
+        <f t="shared" si="0"/>
+        <v>0.18584474885844748</v>
+      </c>
+      <c r="D24" s="32">
+        <f t="shared" si="1"/>
+        <v>185.84474885844747</v>
+      </c>
+      <c r="I24" s="32"/>
+      <c r="J24" s="63"/>
+    </row>
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" s="32">
+        <v>1197</v>
+      </c>
+      <c r="C25" s="32">
+        <f t="shared" si="0"/>
+        <v>0.27328767123287673</v>
+      </c>
+      <c r="D25" s="32">
+        <f t="shared" si="1"/>
+        <v>273.28767123287673</v>
+      </c>
+      <c r="I25" s="32"/>
+      <c r="J25" s="45"/>
+    </row>
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B26" s="63">
+        <v>1181</v>
+      </c>
+      <c r="C26" s="32">
+        <f t="shared" si="0"/>
+        <v>0.26963470319634703</v>
+      </c>
+      <c r="D26" s="32">
+        <f t="shared" si="1"/>
+        <v>269.634703196347</v>
+      </c>
+      <c r="I26" s="32"/>
+    </row>
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="45">
+        <v>1255</v>
+      </c>
+      <c r="C27" s="32">
+        <f t="shared" si="0"/>
+        <v>0.2865296803652968</v>
+      </c>
+      <c r="D27" s="32">
+        <f t="shared" si="1"/>
+        <v>286.52968036529683</v>
+      </c>
+      <c r="I27" s="32"/>
+    </row>
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="B28" s="32">
+        <v>2211</v>
+      </c>
+      <c r="C28" s="32">
+        <f t="shared" si="0"/>
+        <v>0.50479452054794516</v>
+      </c>
+      <c r="D28" s="32">
+        <f t="shared" si="1"/>
+        <v>504.79452054794518</v>
+      </c>
+      <c r="I28" s="32"/>
+    </row>
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="32">
+        <v>7198</v>
+      </c>
+      <c r="C29" s="32">
+        <f t="shared" si="0"/>
+        <v>1.6433789954337898</v>
+      </c>
+      <c r="D29" s="32">
+        <f t="shared" si="1"/>
+        <v>1643.3789954337899</v>
+      </c>
+      <c r="I29" s="32"/>
+    </row>
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="32">
+        <v>14547</v>
+      </c>
+      <c r="C30" s="32">
+        <f t="shared" si="0"/>
+        <v>3.3212328767123287</v>
+      </c>
+      <c r="D30" s="32">
+        <f t="shared" si="1"/>
+        <v>3321.2328767123286</v>
+      </c>
+      <c r="I30" s="32"/>
+    </row>
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="B31" s="32">
+        <v>3142</v>
+      </c>
+      <c r="C31" s="32">
+        <f t="shared" si="0"/>
+        <v>0.71735159817351601</v>
+      </c>
+      <c r="D31" s="32">
+        <f t="shared" si="1"/>
+        <v>717.35159817351598</v>
+      </c>
+      <c r="I31" s="32"/>
+    </row>
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="B32" s="32">
+        <v>846</v>
+      </c>
+      <c r="C32" s="32">
+        <f t="shared" si="0"/>
+        <v>0.19315068493150686</v>
+      </c>
+      <c r="D32" s="32">
+        <f t="shared" si="1"/>
+        <v>193.15068493150687</v>
+      </c>
+      <c r="I32" s="32"/>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="32">
+        <v>1741</v>
+      </c>
+      <c r="C33" s="32">
+        <f t="shared" si="0"/>
+        <v>0.39748858447488583</v>
+      </c>
+      <c r="D33" s="32">
+        <f t="shared" si="1"/>
+        <v>397.48858447488584</v>
+      </c>
+      <c r="I33" s="32"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="32">
+        <v>549</v>
+      </c>
+      <c r="C34" s="32">
+        <f t="shared" si="0"/>
+        <v>0.12534246575342467</v>
+      </c>
+      <c r="D34" s="32">
+        <f t="shared" si="1"/>
+        <v>125.34246575342468</v>
+      </c>
+      <c r="I34" s="32"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="B35" s="32">
+        <v>1363</v>
+      </c>
+      <c r="C35" s="32">
+        <f t="shared" si="0"/>
+        <v>0.31118721461187215</v>
+      </c>
+      <c r="D35" s="32">
+        <f t="shared" si="1"/>
+        <v>311.18721461187215</v>
+      </c>
+      <c r="I35" s="32"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" s="32">
+        <v>6711</v>
+      </c>
+      <c r="C36" s="32">
+        <f t="shared" si="0"/>
+        <v>1.5321917808219179</v>
+      </c>
+      <c r="D36" s="32">
+        <f t="shared" si="1"/>
+        <v>1532.191780821918</v>
+      </c>
+      <c r="I36" s="32"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B37" s="32">
+        <v>3037</v>
+      </c>
+      <c r="C37" s="32">
+        <f t="shared" si="0"/>
+        <v>0.69337899543379</v>
+      </c>
+      <c r="D37" s="32">
+        <f t="shared" si="1"/>
+        <v>693.37899543379001</v>
+      </c>
+      <c r="I37" s="32"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="B38" s="32">
+        <v>347</v>
+      </c>
+      <c r="C38" s="32">
+        <f t="shared" si="0"/>
+        <v>7.9223744292237441E-2</v>
+      </c>
+      <c r="D38" s="32">
+        <f t="shared" si="1"/>
+        <v>79.223744292237441</v>
+      </c>
+      <c r="I38" s="32"/>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="B39" s="32">
+        <v>3046</v>
+      </c>
+      <c r="C39" s="32">
+        <f t="shared" si="0"/>
+        <v>0.69543378995433791</v>
+      </c>
+      <c r="D39" s="32">
+        <f t="shared" si="1"/>
+        <v>695.43378995433795</v>
+      </c>
+      <c r="I39" s="32"/>
+      <c r="J39" s="64"/>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="B40" s="32">
+        <v>3016</v>
+      </c>
+      <c r="C40" s="32">
+        <f t="shared" si="0"/>
+        <v>0.68858447488584473</v>
+      </c>
+      <c r="D40" s="32">
+        <f t="shared" si="1"/>
+        <v>688.58447488584477</v>
+      </c>
+      <c r="I40" s="32"/>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="64">
+        <v>18184</v>
+      </c>
+      <c r="C41" s="32">
+        <f t="shared" si="0"/>
+        <v>4.1515981735159819</v>
+      </c>
+      <c r="D41" s="32">
+        <f t="shared" si="1"/>
+        <v>4151.5981735159821</v>
+      </c>
+      <c r="I41" s="32"/>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" s="32">
+        <v>8368</v>
+      </c>
+      <c r="C42" s="32">
+        <f t="shared" si="0"/>
+        <v>1.9105022831050229</v>
+      </c>
+      <c r="D42" s="32">
+        <f t="shared" si="1"/>
+        <v>1910.5022831050228</v>
+      </c>
+      <c r="I42" s="32"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B43" s="32">
+        <v>59</v>
+      </c>
+      <c r="C43" s="32">
+        <f t="shared" si="0"/>
+        <v>1.3470319634703196E-2</v>
+      </c>
+      <c r="D43" s="32">
+        <f t="shared" si="1"/>
+        <v>13.470319634703197</v>
+      </c>
+      <c r="I43" s="32"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="B44" s="32">
+        <v>1889</v>
+      </c>
+      <c r="C44" s="32">
+        <f t="shared" si="0"/>
+        <v>0.43127853881278538</v>
+      </c>
+      <c r="D44" s="32">
+        <f t="shared" si="1"/>
+        <v>431.27853881278537</v>
+      </c>
+      <c r="I44" s="32"/>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="B45" s="32">
+        <v>1047</v>
+      </c>
+      <c r="C45" s="32">
+        <f t="shared" si="0"/>
+        <v>0.23904109589041095</v>
+      </c>
+      <c r="D45" s="32">
+        <f t="shared" si="1"/>
+        <v>239.04109589041096</v>
+      </c>
+      <c r="I45" s="32"/>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="32">
+        <v>5745</v>
+      </c>
+      <c r="C46" s="32">
+        <f t="shared" si="0"/>
+        <v>1.3116438356164384</v>
+      </c>
+      <c r="D46" s="32">
+        <f t="shared" si="1"/>
+        <v>1311.6438356164383</v>
+      </c>
+      <c r="I46" s="32"/>
+    </row>
+    <row r="47" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B47" s="32">
+        <v>3006</v>
+      </c>
+      <c r="C47" s="32">
+        <f t="shared" si="0"/>
+        <v>0.68630136986301371</v>
+      </c>
+      <c r="D47" s="32">
+        <f t="shared" si="1"/>
+        <v>686.30136986301375</v>
+      </c>
+      <c r="I47" s="32"/>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="B48" s="32">
+        <v>3528</v>
+      </c>
+      <c r="C48" s="32">
+        <f t="shared" si="0"/>
+        <v>0.80547945205479454</v>
+      </c>
+      <c r="D48" s="32">
+        <f t="shared" si="1"/>
+        <v>805.47945205479459</v>
+      </c>
+      <c r="I48" s="32"/>
+    </row>
+    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="B49" s="32">
+        <v>1710</v>
+      </c>
+      <c r="C49" s="32">
+        <f t="shared" si="0"/>
+        <v>0.3904109589041096</v>
+      </c>
+      <c r="D49" s="32">
+        <f t="shared" si="1"/>
+        <v>390.41095890410958</v>
+      </c>
+      <c r="I49" s="32"/>
+    </row>
+    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B50" s="32">
+        <v>3657</v>
+      </c>
+      <c r="C50" s="32">
+        <f t="shared" si="0"/>
+        <v>0.83493150684931505</v>
+      </c>
+      <c r="D50" s="32">
+        <f t="shared" si="1"/>
+        <v>834.93150684931504</v>
+      </c>
+      <c r="I50" s="32"/>
+    </row>
+    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="B51" s="32">
+        <v>27249</v>
+      </c>
+      <c r="C51" s="32">
+        <f t="shared" si="0"/>
+        <v>6.2212328767123291</v>
+      </c>
+      <c r="D51" s="32">
+        <f t="shared" si="1"/>
+        <v>6221.232876712329</v>
+      </c>
+      <c r="I51" s="32"/>
+    </row>
+    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="B52" s="32">
+        <v>4408</v>
+      </c>
+      <c r="C52" s="32">
+        <f t="shared" si="0"/>
+        <v>1.006392694063927</v>
+      </c>
+      <c r="D52" s="32">
+        <f t="shared" si="1"/>
+        <v>1006.3926940639269</v>
+      </c>
+      <c r="I52" s="60"/>
+    </row>
+    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="B53" s="32">
+        <v>2287</v>
+      </c>
+      <c r="C53" s="32">
+        <f t="shared" si="0"/>
+        <v>0.52214611872146122</v>
+      </c>
+      <c r="D53" s="32">
+        <f t="shared" si="1"/>
+        <v>522.14611872146122</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="B54" s="32">
+        <v>4445</v>
+      </c>
+      <c r="C54" s="32">
+        <f t="shared" si="0"/>
+        <v>1.0148401826484019</v>
+      </c>
+      <c r="D54" s="32">
+        <f t="shared" si="1"/>
+        <v>1014.8401826484019</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="50"/>
+    </row>
+    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I58" s="65"/>
+      <c r="J58" s="65"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="65"/>
+      <c r="M58" s="65"/>
+    </row>
+    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I59" s="66"/>
+      <c r="J59" s="67"/>
+      <c r="K59" s="68"/>
+      <c r="L59" s="68"/>
+      <c r="M59" s="69"/>
+    </row>
+    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I60" s="67"/>
+      <c r="J60" s="68"/>
+      <c r="K60" s="68"/>
+      <c r="L60" s="69"/>
+    </row>
+    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I61" s="66"/>
+      <c r="J61" s="67"/>
+      <c r="K61" s="68"/>
+      <c r="L61" s="68"/>
+      <c r="M61" s="69"/>
+    </row>
+    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="B62" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="I62" s="67"/>
+      <c r="J62" s="68"/>
+      <c r="K62" s="68"/>
+      <c r="L62" s="69"/>
+    </row>
+    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="50" t="s">
+        <v>234</v>
+      </c>
+      <c r="B63" s="45"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="H63" s="61" t="s">
+        <v>235</v>
+      </c>
+      <c r="I63" s="51" t="s">
+        <v>236</v>
+      </c>
+      <c r="J63" s="67"/>
+      <c r="K63" s="68"/>
+      <c r="L63" s="68"/>
+      <c r="M63" s="69"/>
+    </row>
+    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="45" t="s">
+        <v>237</v>
+      </c>
+      <c r="B64" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="C64" s="45" t="s">
+        <v>239</v>
+      </c>
+      <c r="D64" s="45" t="s">
+        <v>240</v>
+      </c>
+      <c r="E64" s="45" t="s">
+        <v>241</v>
+      </c>
+      <c r="F64" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="G64" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="J64" s="68"/>
+      <c r="K64" s="68"/>
+      <c r="L64" s="69"/>
+    </row>
+    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="B65" s="45">
+        <f>1050+1093</f>
+        <v>2143</v>
+      </c>
+      <c r="C65" s="45">
+        <f>6161000 + 6272000</f>
+        <v>12433000</v>
+      </c>
+      <c r="D65" s="70">
+        <v>0.67</v>
+      </c>
+      <c r="E65" s="45" t="s">
+        <v>244</v>
+      </c>
+      <c r="F65" s="32">
+        <f>B65/5</f>
+        <v>428.6</v>
+      </c>
+      <c r="G65" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="J65" s="67"/>
+      <c r="K65" s="67"/>
+      <c r="L65" s="68"/>
+      <c r="M65" s="69"/>
+    </row>
+    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="45" t="s">
+        <v>245</v>
+      </c>
+      <c r="B66" s="45">
+        <f>3043+1667</f>
+        <v>4710</v>
+      </c>
+      <c r="C66" s="45">
+        <f>16711000+9234000</f>
+        <v>25945000</v>
+      </c>
+      <c r="D66" s="70">
+        <v>0.63</v>
+      </c>
+      <c r="E66" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="F66" s="32">
+        <f>B66/7</f>
+        <v>672.85714285714289</v>
+      </c>
+      <c r="G66" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="H66" s="32">
+        <f>F77+F78</f>
+        <v>1477.6</v>
+      </c>
+      <c r="I66" s="32" t="s">
+        <v>247</v>
+      </c>
+      <c r="J66" s="68"/>
+      <c r="K66" s="68"/>
+      <c r="L66" s="69"/>
+    </row>
+    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="B67" s="45">
+        <f>1389+1172</f>
+        <v>2561</v>
+      </c>
+      <c r="C67" s="45">
+        <f>7785000+6420000</f>
+        <v>14205000</v>
+      </c>
+      <c r="D67" s="70">
+        <v>0.64</v>
+      </c>
+      <c r="E67" s="45" t="s">
+        <v>249</v>
+      </c>
+      <c r="F67" s="32">
+        <f>B67/6</f>
+        <v>426.83333333333331</v>
+      </c>
+      <c r="G67" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="J67" s="67"/>
+      <c r="K67" s="68"/>
+      <c r="L67" s="68"/>
+      <c r="M67" s="69"/>
+    </row>
+    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="B68" s="45">
+        <f>1160+265</f>
+        <v>1425</v>
+      </c>
+      <c r="C68" s="45">
+        <f>1538000+6906000</f>
+        <v>8444000</v>
+      </c>
+      <c r="D68" s="70">
+        <v>0.68</v>
+      </c>
+      <c r="E68" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="F68" s="32">
+        <f>B68/4</f>
+        <v>356.25</v>
+      </c>
+      <c r="G68" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="J68" s="68"/>
+      <c r="K68" s="68"/>
+      <c r="L68" s="69"/>
+    </row>
+    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="45" t="s">
+        <v>168</v>
+      </c>
+      <c r="B69" s="45">
+        <v>4757</v>
+      </c>
+      <c r="C69" s="45"/>
+      <c r="D69" s="70">
+        <v>0.61</v>
+      </c>
+      <c r="E69" s="45" t="s">
+        <v>252</v>
+      </c>
+      <c r="F69" s="32">
+        <f>B69/6</f>
+        <v>792.83333333333337</v>
+      </c>
+      <c r="G69" s="71" t="s">
+        <v>111</v>
+      </c>
+      <c r="H69" s="32">
+        <f>F78</f>
+        <v>871</v>
+      </c>
+      <c r="I69" s="32" t="s">
+        <v>253</v>
+      </c>
+      <c r="J69" s="67"/>
+      <c r="K69" s="67"/>
+      <c r="L69" s="68"/>
+      <c r="M69" s="69"/>
+    </row>
+    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="45" t="s">
+        <v>182</v>
+      </c>
+      <c r="B70" s="45">
+        <v>1363</v>
+      </c>
+      <c r="C70" s="45"/>
+      <c r="D70" s="70">
+        <v>0.67</v>
+      </c>
+      <c r="E70" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="F70" s="32">
+        <f>B70/2</f>
+        <v>681.5</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="H70" s="32">
+        <f>F66</f>
+        <v>672.85714285714289</v>
+      </c>
+      <c r="I70" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="J70" s="67"/>
+      <c r="K70" s="68"/>
+      <c r="L70" s="69"/>
+    </row>
+    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="B71" s="45">
+        <v>2081</v>
+      </c>
+      <c r="C71" s="45"/>
+      <c r="D71" s="70">
+        <v>0.65</v>
+      </c>
+      <c r="E71" s="45" t="s">
+        <v>256</v>
+      </c>
+      <c r="F71" s="32">
+        <f>B71/5</f>
+        <v>416.2</v>
+      </c>
+      <c r="G71" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="H71" s="32">
+        <f>F66</f>
+        <v>672.85714285714289</v>
+      </c>
+      <c r="I71" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="J71" s="67"/>
+      <c r="K71" s="68"/>
+      <c r="L71" s="68"/>
+      <c r="M71" s="69"/>
+    </row>
+    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="B72" s="45">
+        <f>1741+331</f>
+        <v>2072</v>
+      </c>
+      <c r="C72" s="45"/>
+      <c r="D72" s="70">
+        <v>0.68</v>
+      </c>
+      <c r="E72" s="45" t="s">
+        <v>258</v>
+      </c>
+      <c r="F72" s="32">
+        <f>B72/3</f>
+        <v>690.66666666666663</v>
+      </c>
+      <c r="G72" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="H72" s="32">
+        <f>M126</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="J72" s="68"/>
+      <c r="K72" s="68"/>
+      <c r="L72" s="69"/>
+    </row>
+    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="45" t="s">
+        <v>259</v>
+      </c>
+      <c r="B73" s="45">
+        <f>68+82</f>
+        <v>150</v>
+      </c>
+      <c r="C73" s="45"/>
+      <c r="D73" s="70">
+        <v>0.63</v>
+      </c>
+      <c r="E73" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="F73" s="32">
+        <f>B73/2</f>
+        <v>75</v>
+      </c>
+      <c r="G73" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="J73" s="67"/>
+      <c r="K73" s="68"/>
+      <c r="L73" s="68"/>
+      <c r="M73" s="69"/>
+    </row>
+    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="45">
+        <f>3027+8659</f>
+        <v>11686</v>
+      </c>
+      <c r="C74" s="45"/>
+      <c r="D74" s="70">
+        <v>0.68</v>
+      </c>
+      <c r="E74" s="45" t="s">
+        <v>261</v>
+      </c>
+      <c r="F74" s="32">
+        <f>B74/7</f>
+        <v>1669.4285714285713</v>
+      </c>
+      <c r="G74" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="J74" s="67"/>
+      <c r="K74" s="68"/>
+      <c r="L74" s="69"/>
+    </row>
+    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="45" t="s">
+        <v>262</v>
+      </c>
+      <c r="B75" s="45">
+        <f>395+388</f>
+        <v>783</v>
+      </c>
+      <c r="C75" s="45"/>
+      <c r="D75" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="E75" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="F75" s="32">
+        <f>B75</f>
+        <v>783</v>
+      </c>
+      <c r="G75" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="J75" s="67"/>
+      <c r="K75" s="67"/>
+      <c r="L75" s="68"/>
+      <c r="M75" s="69"/>
+    </row>
+    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="45" t="s">
+        <v>263</v>
+      </c>
+      <c r="B76" s="45">
+        <f>1336+301</f>
+        <v>1637</v>
+      </c>
+      <c r="C76" s="45"/>
+      <c r="D76" s="70">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E76" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="F76" s="32">
+        <f>B76/2</f>
+        <v>818.5</v>
+      </c>
+      <c r="G76" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="H76" s="32">
+        <f>F71</f>
+        <v>416.2</v>
+      </c>
+      <c r="I76" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="J76" s="67"/>
+      <c r="K76" s="68"/>
+      <c r="L76" s="69"/>
+    </row>
+    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="45" t="s">
+        <v>265</v>
+      </c>
+      <c r="B77" s="45">
+        <f>1942+1091</f>
+        <v>3033</v>
+      </c>
+      <c r="C77" s="45"/>
+      <c r="D77" s="70">
+        <v>0.66</v>
+      </c>
+      <c r="E77" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="F77" s="32">
+        <f>B77/5</f>
+        <v>606.6</v>
+      </c>
+      <c r="G77" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="H77" s="63">
+        <v>792.83333330000005</v>
+      </c>
+      <c r="I77" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="J77" s="67"/>
+      <c r="K77" s="68"/>
+      <c r="L77" s="68"/>
+      <c r="M77" s="69"/>
+    </row>
+    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="45" t="s">
+        <v>253</v>
+      </c>
+      <c r="B78" s="45">
+        <f>2166+447</f>
+        <v>2613</v>
+      </c>
+      <c r="C78" s="45"/>
+      <c r="D78" s="70">
+        <v>0.7</v>
+      </c>
+      <c r="E78" s="45" t="s">
+        <v>267</v>
+      </c>
+      <c r="F78" s="32">
+        <f t="shared" ref="F78:F79" si="2">B78/3</f>
+        <v>871</v>
+      </c>
+      <c r="G78" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="J78" s="68"/>
+      <c r="K78" s="68"/>
+      <c r="L78" s="69"/>
+    </row>
+    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="45" t="s">
+        <v>268</v>
+      </c>
+      <c r="B79" s="45">
+        <f>148+416</f>
+        <v>564</v>
+      </c>
+      <c r="C79" s="45"/>
+      <c r="D79" s="70">
+        <v>0.65</v>
+      </c>
+      <c r="E79" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="F79" s="32">
+        <f t="shared" si="2"/>
+        <v>188</v>
+      </c>
+      <c r="G79" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="J79" s="67"/>
+      <c r="K79" s="68"/>
+      <c r="L79" s="68"/>
+      <c r="M79" s="69"/>
+    </row>
+    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="45" t="s">
+        <v>270</v>
+      </c>
+      <c r="B80" s="45">
+        <f>15997+9228</f>
+        <v>25225</v>
+      </c>
+      <c r="C80" s="45"/>
+      <c r="D80" s="70">
+        <v>0.69</v>
+      </c>
+      <c r="E80" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="F80" s="32">
+        <f>B80/4</f>
+        <v>6306.25</v>
+      </c>
+      <c r="G80" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="J80" s="68"/>
+      <c r="K80" s="68"/>
+      <c r="L80" s="69"/>
+    </row>
+    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="B81" s="45">
+        <f>4029+3025</f>
+        <v>7054</v>
+      </c>
+      <c r="C81" s="45"/>
+      <c r="D81" s="70">
+        <v>0.63</v>
+      </c>
+      <c r="E81" s="72" t="s">
+        <v>110</v>
+      </c>
+      <c r="F81" s="32">
+        <f t="shared" ref="F81:F83" si="3">B81</f>
+        <v>7054</v>
+      </c>
+      <c r="G81" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="J81" s="67"/>
+      <c r="K81" s="67"/>
+      <c r="L81" s="68"/>
+      <c r="M81" s="69"/>
+    </row>
+    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="B82" s="45">
+        <v>4723</v>
+      </c>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="E82" s="45"/>
+      <c r="F82" s="32">
+        <f t="shared" si="3"/>
+        <v>4723</v>
+      </c>
+      <c r="G82" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="H82" s="32">
+        <f t="shared" ref="H82:H83" si="4">F65</f>
+        <v>428.6</v>
+      </c>
+      <c r="I82" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="J82" s="67"/>
+      <c r="K82" s="68"/>
+      <c r="L82" s="69"/>
+    </row>
+    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="B83" s="45">
+        <v>145</v>
+      </c>
+      <c r="C83" s="45"/>
+      <c r="D83" s="70">
+        <v>0.53</v>
+      </c>
+      <c r="E83" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="F83" s="32">
+        <f t="shared" si="3"/>
+        <v>145</v>
+      </c>
+      <c r="G83" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="H83" s="32">
+        <f t="shared" si="4"/>
+        <v>672.85714285714289</v>
+      </c>
+      <c r="I83" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="J83" s="67"/>
+      <c r="K83" s="68"/>
+      <c r="L83" s="68"/>
+      <c r="M83" s="69"/>
+    </row>
+    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="I84" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="J84" s="67"/>
+      <c r="K84" s="68"/>
+      <c r="L84" s="69"/>
+    </row>
+    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G85" s="71" t="s">
+        <v>143</v>
+      </c>
+      <c r="H85" s="63">
+        <f>F68</f>
+        <v>356.25</v>
+      </c>
+      <c r="I85" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="J85" s="67"/>
+      <c r="K85" s="68"/>
+      <c r="L85" s="68"/>
+      <c r="M85" s="69"/>
+    </row>
+    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G86" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="H86" s="45">
+        <f>F73+F71</f>
+        <v>491.2</v>
+      </c>
+      <c r="I86" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="J86" s="68"/>
+      <c r="K86" s="68"/>
+      <c r="L86" s="69"/>
+    </row>
+    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G87" s="32" t="s">
+        <v>146</v>
+      </c>
+      <c r="J87" s="67"/>
+      <c r="K87" s="68"/>
+      <c r="L87" s="68"/>
+      <c r="M87" s="69"/>
+    </row>
+    <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G88" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="J88" s="67"/>
+      <c r="K88" s="68"/>
+      <c r="L88" s="69"/>
+    </row>
+    <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G89" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="J89" s="67"/>
+      <c r="K89" s="67"/>
+      <c r="L89" s="68"/>
+      <c r="M89" s="69"/>
+    </row>
+    <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G90" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="J90" s="67"/>
+      <c r="K90" s="68"/>
+      <c r="L90" s="69"/>
+    </row>
+    <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G91" s="71" t="s">
+        <v>154</v>
+      </c>
+      <c r="H91" s="32">
+        <f>F78+F79</f>
+        <v>1059</v>
+      </c>
+      <c r="I91" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="J91" s="67"/>
+      <c r="K91" s="68"/>
+      <c r="L91" s="68"/>
+      <c r="M91" s="69"/>
+    </row>
+    <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G92" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="I92" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="J92" s="68"/>
+      <c r="K92" s="68"/>
+      <c r="L92" s="69"/>
+    </row>
+    <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G93" s="71" t="s">
+        <v>158</v>
+      </c>
+      <c r="H93" s="32">
+        <f>F66</f>
+        <v>672.85714285714289</v>
+      </c>
+      <c r="I93" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="J93" s="67"/>
+      <c r="K93" s="68"/>
+      <c r="L93" s="68"/>
+      <c r="M93" s="69"/>
+    </row>
+    <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G94" s="71" t="s">
+        <v>160</v>
+      </c>
+      <c r="H94" s="32">
+        <f>F78+F79</f>
+        <v>1059</v>
+      </c>
+      <c r="I94" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="J94" s="68"/>
+      <c r="K94" s="68"/>
+      <c r="L94" s="69"/>
+    </row>
+    <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G95" s="32" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G96" s="71" t="s">
+        <v>164</v>
+      </c>
+      <c r="H96" s="32">
+        <f>+F67+F70</f>
+        <v>1108.3333333333333</v>
+      </c>
+      <c r="I96" s="45" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G97" s="32" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G98" s="71" t="s">
+        <v>168</v>
+      </c>
+      <c r="H98" s="32">
+        <f>F68+F69</f>
+        <v>1149.0833333333335</v>
+      </c>
+      <c r="I98" s="32" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="99" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G99" s="32" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="100" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G100" s="71" t="s">
+        <v>172</v>
+      </c>
+      <c r="H100" s="64">
+        <f>F80</f>
+        <v>6306.25</v>
+      </c>
+      <c r="I100" s="45" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="101" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G101" s="71" t="s">
+        <v>174</v>
+      </c>
+      <c r="H101" s="32">
+        <f>F66+F69</f>
+        <v>1465.6904761904761</v>
+      </c>
+      <c r="I101" s="32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="102" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G102" s="32" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="103" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G103" s="32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="104" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G104" s="32" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="105" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G105" s="32" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="106" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G106" s="71" t="s">
+        <v>184</v>
+      </c>
+      <c r="H106" s="32">
+        <f>F75+F76</f>
+        <v>1601.5</v>
+      </c>
+      <c r="I106" s="73" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="107" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G107" s="32" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="108" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G108" s="32" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="109" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G109" s="71" t="s">
+        <v>190</v>
+      </c>
+      <c r="H109" s="32">
+        <f>F66+F69</f>
+        <v>1465.6904761904761</v>
+      </c>
+      <c r="I109" s="32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="110" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G110" s="32" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="111" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G111" s="32" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="112" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G112" s="71" t="s">
+        <v>196</v>
+      </c>
+      <c r="H112" s="32">
+        <f>F68+F71</f>
+        <v>772.45</v>
+      </c>
+      <c r="I112" s="32" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="113" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G113" s="60" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="114" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B62" r:id="rId1" xr:uid="{31584BB2-B7E7-4133-B487-37CDDD4F8072}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2613,7 +5483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
@@ -2638,7 +5508,7 @@
         <v>54</v>
       </c>
       <c r="B2" s="14">
-        <f>9*10^12</f>
+        <f>IF(INDEX('coal ban'!D:D,MATCH(About!$B$2,'coal ban'!C:C,0))="yes",0,9*10^12)</f>
         <v>9000000000000</v>
       </c>
     </row>
@@ -2665,8 +5535,7 @@
         <v>36</v>
       </c>
       <c r="B5" s="14">
-        <f>9*10^12</f>
-        <v>9000000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2818,7 +5687,7 @@
         <v>95</v>
       </c>
       <c r="B22" s="14">
-        <f>9*10^12</f>
+        <f>IF(INDEX('coal ban'!D:D,MATCH(About!$B$2,'coal ban'!C:C,0))="yes",0,9*10^12)</f>
         <v>9000000000000</v>
       </c>
     </row>
@@ -2856,6 +5725,577 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C333C710-6A53-4C92-917A-049B0A9C4CC8}">
+  <dimension ref="B1:D51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B1" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="27" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="27" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>112</v>
+      </c>
+      <c r="D7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="D8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="27" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="27" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D11" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="27" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="D15" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="D17" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="27" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="D22" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="27" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="C28" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="D28" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="27" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="27" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C31" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="D32" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C34" s="27" t="s">
+        <v>165</v>
+      </c>
+      <c r="D34" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="27" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="27" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="27" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="C37" s="27" t="s">
+        <v>171</v>
+      </c>
+      <c r="D37" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="D38" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>175</v>
+      </c>
+      <c r="D39" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="27" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="27" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="27" t="s">
+        <v>180</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>181</v>
+      </c>
+      <c r="D42" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>183</v>
+      </c>
+      <c r="D43" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="D44" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C45" s="27" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="27" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="D46" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="C47" s="27" t="s">
+        <v>191</v>
+      </c>
+      <c r="D47" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="27" t="s">
+        <v>192</v>
+      </c>
+      <c r="C48" s="27" t="s">
+        <v>193</v>
+      </c>
+      <c r="D48" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="C49" s="27" t="s">
+        <v>195</v>
+      </c>
+      <c r="D49" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="27" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="D50" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" t="s">
+        <v>281</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B87394CF-62EC-4069-88FA-A4FFA79125F2}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -4264,7 +7704,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D532E82F-DE71-433C-A904-F547FC46FF0C}">
   <dimension ref="A1:J1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6279,7 +9719,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3FE3131-58B4-4490-BBBD-7F1C79BC2A36}">
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -6909,1512 +10349,6 @@
       <c r="C53" s="47">
         <f t="shared" si="0"/>
         <v>1956000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="50" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DC60A1-9DC3-4CCB-9E47-F7E8824CC567}">
-  <dimension ref="A1:C1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="26" width="8.7109375" style="28" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="28"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="str">
-        <f>About!B2</f>
-        <v>WI</v>
-      </c>
-      <c r="B1" s="32">
-        <f>SUMIFS(C4:C53,A4:A53,A1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
-        <v>100</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="32" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="47">
-        <f t="shared" ref="C4:C53" si="0">B4*1000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" s="32">
-        <v>655</v>
-      </c>
-      <c r="C8" s="47">
-        <f t="shared" si="0"/>
-        <v>655000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="C9" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" s="32">
-        <v>7</v>
-      </c>
-      <c r="C10" s="47">
-        <f t="shared" si="0"/>
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="B11" s="32">
-        <v>15</v>
-      </c>
-      <c r="C11" s="47">
-        <f t="shared" si="0"/>
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="B12" s="32">
-        <v>10</v>
-      </c>
-      <c r="C12" s="47">
-        <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="32">
-        <v>16</v>
-      </c>
-      <c r="C16" s="47">
-        <f t="shared" si="0"/>
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B21" s="32">
-        <v>341</v>
-      </c>
-      <c r="C21" s="47">
-        <f t="shared" si="0"/>
-        <v>341000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22" s="32">
-        <v>147</v>
-      </c>
-      <c r="C22" s="47">
-        <f t="shared" si="0"/>
-        <v>147000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B23" s="32">
-        <v>52</v>
-      </c>
-      <c r="C23" s="47">
-        <f t="shared" si="0"/>
-        <v>52000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="B24" s="32">
-        <v>184</v>
-      </c>
-      <c r="C24" s="47">
-        <f t="shared" si="0"/>
-        <v>184000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" s="32">
-        <v>423</v>
-      </c>
-      <c r="C25" s="47">
-        <f t="shared" si="0"/>
-        <v>423000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="B26" s="32">
-        <v>29</v>
-      </c>
-      <c r="C26" s="47">
-        <f t="shared" si="0"/>
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="B27" s="32">
-        <v>3</v>
-      </c>
-      <c r="C27" s="47">
-        <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="C28" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="C30" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="C31" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="B32" s="32">
-        <v>3</v>
-      </c>
-      <c r="C32" s="47">
-        <f t="shared" si="0"/>
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="B33" s="32">
-        <v>102</v>
-      </c>
-      <c r="C33" s="47">
-        <f t="shared" si="0"/>
-        <v>102000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="C34" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="B35" s="32">
-        <v>146</v>
-      </c>
-      <c r="C35" s="47">
-        <f t="shared" si="0"/>
-        <v>146000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="B36" s="32">
-        <v>306</v>
-      </c>
-      <c r="C36" s="47">
-        <f t="shared" si="0"/>
-        <v>306000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="C37" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="B38" s="32">
-        <v>42</v>
-      </c>
-      <c r="C38" s="47">
-        <f t="shared" si="0"/>
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="C39" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="B40" s="32">
-        <v>225</v>
-      </c>
-      <c r="C40" s="47">
-        <f t="shared" si="0"/>
-        <v>225000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="B41" s="32">
-        <v>6</v>
-      </c>
-      <c r="C41" s="47">
-        <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="45" t="s">
-        <v>177</v>
-      </c>
-      <c r="B42" s="32">
-        <v>21</v>
-      </c>
-      <c r="C42" s="47">
-        <f t="shared" si="0"/>
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="B43" s="32">
-        <v>133</v>
-      </c>
-      <c r="C43" s="47">
-        <f t="shared" si="0"/>
-        <v>133000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="C44" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
-        <v>183</v>
-      </c>
-      <c r="C45" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="B46" s="32">
-        <v>271</v>
-      </c>
-      <c r="C46" s="47">
-        <f t="shared" si="0"/>
-        <v>271000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="45" t="s">
-        <v>187</v>
-      </c>
-      <c r="C47" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="C48" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="B49" s="32">
-        <v>89</v>
-      </c>
-      <c r="C49" s="47">
-        <f t="shared" si="0"/>
-        <v>89000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="C50" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="C51" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="C52" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="C53" s="47">
-        <f t="shared" si="0"/>
-        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9375,6 +11309,1512 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6DC60A1-9DC3-4CCB-9E47-F7E8824CC567}">
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="26" width="8.7109375" style="28" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="str">
+        <f>About!B2</f>
+        <v>WI</v>
+      </c>
+      <c r="B1" s="32">
+        <f>SUMIFS(C4:C53,A4:A53,A1)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="45" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="45" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="47">
+        <f t="shared" ref="C4:C53" si="0">B4*1000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="45" t="s">
+        <v>108</v>
+      </c>
+      <c r="C7" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="32">
+        <v>655</v>
+      </c>
+      <c r="C8" s="47">
+        <f t="shared" si="0"/>
+        <v>655000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C9" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="32">
+        <v>7</v>
+      </c>
+      <c r="C10" s="47">
+        <f t="shared" si="0"/>
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="B11" s="32">
+        <v>15</v>
+      </c>
+      <c r="C11" s="47">
+        <f t="shared" si="0"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="45" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" s="32">
+        <v>10</v>
+      </c>
+      <c r="C12" s="47">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="45" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="32">
+        <v>16</v>
+      </c>
+      <c r="C16" s="47">
+        <f t="shared" si="0"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B21" s="32">
+        <v>341</v>
+      </c>
+      <c r="C21" s="47">
+        <f t="shared" si="0"/>
+        <v>341000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="45" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="32">
+        <v>147</v>
+      </c>
+      <c r="C22" s="47">
+        <f t="shared" si="0"/>
+        <v>147000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="45" t="s">
+        <v>140</v>
+      </c>
+      <c r="B23" s="32">
+        <v>52</v>
+      </c>
+      <c r="C23" s="47">
+        <f t="shared" si="0"/>
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="45" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="32">
+        <v>184</v>
+      </c>
+      <c r="C24" s="47">
+        <f t="shared" si="0"/>
+        <v>184000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="45" t="s">
+        <v>144</v>
+      </c>
+      <c r="B25" s="32">
+        <v>423</v>
+      </c>
+      <c r="C25" s="47">
+        <f t="shared" si="0"/>
+        <v>423000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="32">
+        <v>29</v>
+      </c>
+      <c r="C26" s="47">
+        <f t="shared" si="0"/>
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="45" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="32">
+        <v>3</v>
+      </c>
+      <c r="C27" s="47">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="45" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="45" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="45" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="45" t="s">
+        <v>157</v>
+      </c>
+      <c r="B32" s="32">
+        <v>3</v>
+      </c>
+      <c r="C32" s="47">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="45" t="s">
+        <v>159</v>
+      </c>
+      <c r="B33" s="32">
+        <v>102</v>
+      </c>
+      <c r="C33" s="47">
+        <f t="shared" si="0"/>
+        <v>102000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="C34" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="45" t="s">
+        <v>163</v>
+      </c>
+      <c r="B35" s="32">
+        <v>146</v>
+      </c>
+      <c r="C35" s="47">
+        <f t="shared" si="0"/>
+        <v>146000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="45" t="s">
+        <v>165</v>
+      </c>
+      <c r="B36" s="32">
+        <v>306</v>
+      </c>
+      <c r="C36" s="47">
+        <f t="shared" si="0"/>
+        <v>306000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="45" t="s">
+        <v>167</v>
+      </c>
+      <c r="C37" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="45" t="s">
+        <v>169</v>
+      </c>
+      <c r="B38" s="32">
+        <v>42</v>
+      </c>
+      <c r="C38" s="47">
+        <f t="shared" si="0"/>
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="C39" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="32">
+        <v>225</v>
+      </c>
+      <c r="C40" s="47">
+        <f t="shared" si="0"/>
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="B41" s="32">
+        <v>6</v>
+      </c>
+      <c r="C41" s="47">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B42" s="32">
+        <v>21</v>
+      </c>
+      <c r="C42" s="47">
+        <f t="shared" si="0"/>
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="B43" s="32">
+        <v>133</v>
+      </c>
+      <c r="C43" s="47">
+        <f t="shared" si="0"/>
+        <v>133000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="C44" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="45" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="45" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46" s="32">
+        <v>271</v>
+      </c>
+      <c r="C46" s="47">
+        <f t="shared" si="0"/>
+        <v>271000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="C47" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="C48" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B49" s="32">
+        <v>89</v>
+      </c>
+      <c r="C49" s="47">
+        <f t="shared" si="0"/>
+        <v>89000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="C50" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="C51" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="C52" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="C53" s="47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="50" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{433B8708-1261-466E-BB3B-9EFA88068AF6}">
   <dimension ref="A1:N1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -12596,7 +16036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2113D23D-A062-4A17-A3A9-D14A938B4B23}">
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -14393,7 +17833,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18CB9D0F-F59F-4121-AE69-825DCCA06CD7}">
   <dimension ref="A1:F1000"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -15985,2864 +19425,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034993D7-C303-48FF-99F6-02F9737AB03C}">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="13.7109375" style="28" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="28" customWidth="1"/>
-    <col min="5" max="5" width="22.42578125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="28" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" style="28" customWidth="1"/>
-    <col min="8" max="8" width="23.5703125" style="28" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" style="28" customWidth="1"/>
-    <col min="10" max="10" width="22.28515625" style="28" customWidth="1"/>
-    <col min="11" max="11" width="21.140625" style="28" customWidth="1"/>
-    <col min="12" max="26" width="8.7109375" style="28" customWidth="1"/>
-    <col min="27" max="16384" width="14.42578125" style="28"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="32" t="str">
-        <f>About!B2</f>
-        <v>WI</v>
-      </c>
-      <c r="B1" s="32">
-        <f>SUMIFS(D5:D54,A5:A54,A1)</f>
-        <v>522.14611872146122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="60" t="s">
-        <v>226</v>
-      </c>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="60"/>
-      <c r="I2" s="51"/>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="G3" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="I3" s="32"/>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="B4" s="61" t="s">
-        <v>230</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="51"/>
-      <c r="F4" s="32">
-        <f>8760*0.5</f>
-        <v>4380</v>
-      </c>
-      <c r="G4" s="62" t="s">
-        <v>231</v>
-      </c>
-      <c r="I4" s="32"/>
-    </row>
-    <row r="5" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="32">
-        <v>4103</v>
-      </c>
-      <c r="C5" s="32">
-        <f t="shared" ref="C5:C54" si="0">B5/$F$4</f>
-        <v>0.93675799086757994</v>
-      </c>
-      <c r="D5" s="32">
-        <f t="shared" ref="D5:D54" si="1">C5*1000</f>
-        <v>936.75799086757991</v>
-      </c>
-      <c r="I5" s="32"/>
-    </row>
-    <row r="6" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="32">
-        <v>23676</v>
-      </c>
-      <c r="C6" s="32">
-        <f t="shared" si="0"/>
-        <v>5.4054794520547942</v>
-      </c>
-      <c r="D6" s="32">
-        <f t="shared" si="1"/>
-        <v>5405.4794520547939</v>
-      </c>
-      <c r="I6" s="32"/>
-    </row>
-    <row r="7" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="32">
-        <v>1303</v>
-      </c>
-      <c r="C7" s="32">
-        <f t="shared" si="0"/>
-        <v>0.29748858447488585</v>
-      </c>
-      <c r="D7" s="32">
-        <f t="shared" si="1"/>
-        <v>297.48858447488584</v>
-      </c>
-      <c r="I7" s="32"/>
-    </row>
-    <row r="8" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="45" t="s">
-        <v>108</v>
-      </c>
-      <c r="B8" s="32">
-        <v>6093</v>
-      </c>
-      <c r="C8" s="32">
-        <f t="shared" si="0"/>
-        <v>1.3910958904109589</v>
-      </c>
-      <c r="D8" s="32">
-        <f t="shared" si="1"/>
-        <v>1391.0958904109589</v>
-      </c>
-      <c r="I8" s="32"/>
-    </row>
-    <row r="9" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="32">
-        <v>30024</v>
-      </c>
-      <c r="C9" s="32">
-        <f t="shared" si="0"/>
-        <v>6.8547945205479452</v>
-      </c>
-      <c r="D9" s="32">
-        <f t="shared" si="1"/>
-        <v>6854.7945205479455</v>
-      </c>
-      <c r="I9" s="32"/>
-    </row>
-    <row r="10" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="B10" s="32">
-        <v>7789</v>
-      </c>
-      <c r="C10" s="32">
-        <f t="shared" si="0"/>
-        <v>1.7783105022831049</v>
-      </c>
-      <c r="D10" s="32">
-        <f t="shared" si="1"/>
-        <v>1778.3105022831051</v>
-      </c>
-      <c r="I10" s="32"/>
-    </row>
-    <row r="11" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" s="32">
-        <v>922</v>
-      </c>
-      <c r="C11" s="32">
-        <f t="shared" si="0"/>
-        <v>0.21050228310502284</v>
-      </c>
-      <c r="D11" s="32">
-        <f t="shared" si="1"/>
-        <v>210.50228310502283</v>
-      </c>
-      <c r="I11" s="32"/>
-    </row>
-    <row r="12" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="45" t="s">
-        <v>116</v>
-      </c>
-      <c r="B12" s="32">
-        <v>31</v>
-      </c>
-      <c r="C12" s="32">
-        <f t="shared" si="0"/>
-        <v>7.0776255707762558E-3</v>
-      </c>
-      <c r="D12" s="32">
-        <f t="shared" si="1"/>
-        <v>7.0776255707762559</v>
-      </c>
-      <c r="I12" s="32"/>
-    </row>
-    <row r="13" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="45" t="s">
-        <v>118</v>
-      </c>
-      <c r="B13" s="32">
-        <v>682</v>
-      </c>
-      <c r="C13" s="32">
-        <f t="shared" si="0"/>
-        <v>0.15570776255707763</v>
-      </c>
-      <c r="D13" s="32">
-        <f t="shared" si="1"/>
-        <v>155.70776255707764</v>
-      </c>
-      <c r="I13" s="32"/>
-    </row>
-    <row r="14" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="32">
-        <v>1988</v>
-      </c>
-      <c r="C14" s="32">
-        <f t="shared" si="0"/>
-        <v>0.45388127853881277</v>
-      </c>
-      <c r="D14" s="32">
-        <f t="shared" si="1"/>
-        <v>453.88127853881275</v>
-      </c>
-      <c r="I14" s="32"/>
-    </row>
-    <row r="15" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="B15" s="32">
-        <v>2602</v>
-      </c>
-      <c r="C15" s="32">
-        <f t="shared" si="0"/>
-        <v>0.59406392694063925</v>
-      </c>
-      <c r="D15" s="32">
-        <f t="shared" si="1"/>
-        <v>594.06392694063925</v>
-      </c>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="32"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="32"/>
-      <c r="O15" s="32"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="32"/>
-      <c r="R15" s="32"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="32"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="32"/>
-      <c r="X15" s="32"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="32"/>
-    </row>
-    <row r="16" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="45" t="s">
-        <v>124</v>
-      </c>
-      <c r="B16" s="32">
-        <v>18758</v>
-      </c>
-      <c r="C16" s="32">
-        <f t="shared" si="0"/>
-        <v>4.2826484018264841</v>
-      </c>
-      <c r="D16" s="32">
-        <f t="shared" si="1"/>
-        <v>4282.6484018264837</v>
-      </c>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="63"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="32"/>
-      <c r="O16" s="32"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="32"/>
-      <c r="R16" s="32"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="32"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="32"/>
-      <c r="X16" s="32"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="32"/>
-    </row>
-    <row r="17" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="32">
-        <v>4883</v>
-      </c>
-      <c r="C17" s="32">
-        <f t="shared" si="0"/>
-        <v>1.1148401826484018</v>
-      </c>
-      <c r="D17" s="32">
-        <f t="shared" si="1"/>
-        <v>1114.8401826484019</v>
-      </c>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="32"/>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="32"/>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-    </row>
-    <row r="18" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="45" t="s">
-        <v>128</v>
-      </c>
-      <c r="B18" s="63">
-        <v>2394</v>
-      </c>
-      <c r="C18" s="32">
-        <f t="shared" si="0"/>
-        <v>0.54657534246575346</v>
-      </c>
-      <c r="D18" s="32">
-        <f t="shared" si="1"/>
-        <v>546.57534246575347</v>
-      </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="32"/>
-      <c r="O18" s="32"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="32"/>
-      <c r="R18" s="32"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="32"/>
-      <c r="U18" s="32"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="32"/>
-      <c r="X18" s="32"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="32"/>
-    </row>
-    <row r="19" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="B19" s="32">
-        <v>2818</v>
-      </c>
-      <c r="C19" s="32">
-        <f t="shared" si="0"/>
-        <v>0.64337899543378996</v>
-      </c>
-      <c r="D19" s="32">
-        <f t="shared" si="1"/>
-        <v>643.37899543379001</v>
-      </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="32"/>
-      <c r="L19" s="32"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="32"/>
-      <c r="O19" s="32"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="32"/>
-      <c r="R19" s="32"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="32"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="32"/>
-      <c r="X19" s="32"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="32"/>
-    </row>
-    <row r="20" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="45" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="32">
-        <v>2508</v>
-      </c>
-      <c r="C20" s="32">
-        <f t="shared" si="0"/>
-        <v>0.57260273972602738</v>
-      </c>
-      <c r="D20" s="32">
-        <f t="shared" si="1"/>
-        <v>572.60273972602738</v>
-      </c>
-      <c r="I20" s="32"/>
-    </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="B21" s="32">
-        <v>4255</v>
-      </c>
-      <c r="C21" s="32">
-        <f t="shared" si="0"/>
-        <v>0.97146118721461183</v>
-      </c>
-      <c r="D21" s="32">
-        <f t="shared" si="1"/>
-        <v>971.46118721461187</v>
-      </c>
-      <c r="I21" s="32"/>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="45" t="s">
-        <v>136</v>
-      </c>
-      <c r="B22" s="32">
-        <v>2423</v>
-      </c>
-      <c r="C22" s="32">
-        <f t="shared" si="0"/>
-        <v>0.55319634703196352</v>
-      </c>
-      <c r="D22" s="32">
-        <f t="shared" si="1"/>
-        <v>553.19634703196357</v>
-      </c>
-      <c r="I22" s="32"/>
-    </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="45" t="s">
-        <v>138</v>
-      </c>
-      <c r="B23" s="32">
-        <v>3916</v>
-      </c>
-      <c r="C23" s="32">
-        <f t="shared" si="0"/>
-        <v>0.8940639269406393</v>
-      </c>
-      <c r="D23" s="32">
-        <f t="shared" si="1"/>
-        <v>894.06392694063925</v>
-      </c>
-      <c r="I23" s="32"/>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="45" t="s">
-        <v>140</v>
-      </c>
-      <c r="B24" s="32">
-        <v>814</v>
-      </c>
-      <c r="C24" s="32">
-        <f t="shared" si="0"/>
-        <v>0.18584474885844748</v>
-      </c>
-      <c r="D24" s="32">
-        <f t="shared" si="1"/>
-        <v>185.84474885844747</v>
-      </c>
-      <c r="I24" s="32"/>
-      <c r="J24" s="63"/>
-    </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="45" t="s">
-        <v>142</v>
-      </c>
-      <c r="B25" s="32">
-        <v>1197</v>
-      </c>
-      <c r="C25" s="32">
-        <f t="shared" si="0"/>
-        <v>0.27328767123287673</v>
-      </c>
-      <c r="D25" s="32">
-        <f t="shared" si="1"/>
-        <v>273.28767123287673</v>
-      </c>
-      <c r="I25" s="32"/>
-      <c r="J25" s="45"/>
-    </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
-        <v>144</v>
-      </c>
-      <c r="B26" s="63">
-        <v>1181</v>
-      </c>
-      <c r="C26" s="32">
-        <f t="shared" si="0"/>
-        <v>0.26963470319634703</v>
-      </c>
-      <c r="D26" s="32">
-        <f t="shared" si="1"/>
-        <v>269.634703196347</v>
-      </c>
-      <c r="I26" s="32"/>
-    </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45" t="s">
-        <v>145</v>
-      </c>
-      <c r="B27" s="45">
-        <v>1255</v>
-      </c>
-      <c r="C27" s="32">
-        <f t="shared" si="0"/>
-        <v>0.2865296803652968</v>
-      </c>
-      <c r="D27" s="32">
-        <f t="shared" si="1"/>
-        <v>286.52968036529683</v>
-      </c>
-      <c r="I27" s="32"/>
-    </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="45" t="s">
-        <v>147</v>
-      </c>
-      <c r="B28" s="32">
-        <v>2211</v>
-      </c>
-      <c r="C28" s="32">
-        <f t="shared" si="0"/>
-        <v>0.50479452054794516</v>
-      </c>
-      <c r="D28" s="32">
-        <f t="shared" si="1"/>
-        <v>504.79452054794518</v>
-      </c>
-      <c r="I28" s="32"/>
-    </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="B29" s="32">
-        <v>7198</v>
-      </c>
-      <c r="C29" s="32">
-        <f t="shared" si="0"/>
-        <v>1.6433789954337898</v>
-      </c>
-      <c r="D29" s="32">
-        <f t="shared" si="1"/>
-        <v>1643.3789954337899</v>
-      </c>
-      <c r="I29" s="32"/>
-    </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="45" t="s">
-        <v>151</v>
-      </c>
-      <c r="B30" s="32">
-        <v>14547</v>
-      </c>
-      <c r="C30" s="32">
-        <f t="shared" si="0"/>
-        <v>3.3212328767123287</v>
-      </c>
-      <c r="D30" s="32">
-        <f t="shared" si="1"/>
-        <v>3321.2328767123286</v>
-      </c>
-      <c r="I30" s="32"/>
-    </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="45" t="s">
-        <v>153</v>
-      </c>
-      <c r="B31" s="32">
-        <v>3142</v>
-      </c>
-      <c r="C31" s="32">
-        <f t="shared" si="0"/>
-        <v>0.71735159817351601</v>
-      </c>
-      <c r="D31" s="32">
-        <f t="shared" si="1"/>
-        <v>717.35159817351598</v>
-      </c>
-      <c r="I31" s="32"/>
-    </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="45" t="s">
-        <v>155</v>
-      </c>
-      <c r="B32" s="32">
-        <v>846</v>
-      </c>
-      <c r="C32" s="32">
-        <f t="shared" si="0"/>
-        <v>0.19315068493150686</v>
-      </c>
-      <c r="D32" s="32">
-        <f t="shared" si="1"/>
-        <v>193.15068493150687</v>
-      </c>
-      <c r="I32" s="32"/>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="45" t="s">
-        <v>157</v>
-      </c>
-      <c r="B33" s="32">
-        <v>1741</v>
-      </c>
-      <c r="C33" s="32">
-        <f t="shared" si="0"/>
-        <v>0.39748858447488583</v>
-      </c>
-      <c r="D33" s="32">
-        <f t="shared" si="1"/>
-        <v>397.48858447488584</v>
-      </c>
-      <c r="I33" s="32"/>
-    </row>
-    <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="B34" s="32">
-        <v>549</v>
-      </c>
-      <c r="C34" s="32">
-        <f t="shared" si="0"/>
-        <v>0.12534246575342467</v>
-      </c>
-      <c r="D34" s="32">
-        <f t="shared" si="1"/>
-        <v>125.34246575342468</v>
-      </c>
-      <c r="I34" s="32"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="45" t="s">
-        <v>161</v>
-      </c>
-      <c r="B35" s="32">
-        <v>1363</v>
-      </c>
-      <c r="C35" s="32">
-        <f t="shared" si="0"/>
-        <v>0.31118721461187215</v>
-      </c>
-      <c r="D35" s="32">
-        <f t="shared" si="1"/>
-        <v>311.18721461187215</v>
-      </c>
-      <c r="I35" s="32"/>
-    </row>
-    <row r="36" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="45" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" s="32">
-        <v>6711</v>
-      </c>
-      <c r="C36" s="32">
-        <f t="shared" si="0"/>
-        <v>1.5321917808219179</v>
-      </c>
-      <c r="D36" s="32">
-        <f t="shared" si="1"/>
-        <v>1532.191780821918</v>
-      </c>
-      <c r="I36" s="32"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="45" t="s">
-        <v>165</v>
-      </c>
-      <c r="B37" s="32">
-        <v>3037</v>
-      </c>
-      <c r="C37" s="32">
-        <f t="shared" si="0"/>
-        <v>0.69337899543379</v>
-      </c>
-      <c r="D37" s="32">
-        <f t="shared" si="1"/>
-        <v>693.37899543379001</v>
-      </c>
-      <c r="I37" s="32"/>
-    </row>
-    <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="45" t="s">
-        <v>167</v>
-      </c>
-      <c r="B38" s="32">
-        <v>347</v>
-      </c>
-      <c r="C38" s="32">
-        <f t="shared" si="0"/>
-        <v>7.9223744292237441E-2</v>
-      </c>
-      <c r="D38" s="32">
-        <f t="shared" si="1"/>
-        <v>79.223744292237441</v>
-      </c>
-      <c r="I38" s="32"/>
-    </row>
-    <row r="39" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="45" t="s">
-        <v>169</v>
-      </c>
-      <c r="B39" s="32">
-        <v>3046</v>
-      </c>
-      <c r="C39" s="32">
-        <f t="shared" si="0"/>
-        <v>0.69543378995433791</v>
-      </c>
-      <c r="D39" s="32">
-        <f t="shared" si="1"/>
-        <v>695.43378995433795</v>
-      </c>
-      <c r="I39" s="32"/>
-      <c r="J39" s="64"/>
-    </row>
-    <row r="40" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="B40" s="32">
-        <v>3016</v>
-      </c>
-      <c r="C40" s="32">
-        <f t="shared" si="0"/>
-        <v>0.68858447488584473</v>
-      </c>
-      <c r="D40" s="32">
-        <f t="shared" si="1"/>
-        <v>688.58447488584477</v>
-      </c>
-      <c r="I40" s="32"/>
-    </row>
-    <row r="41" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="B41" s="64">
-        <v>18184</v>
-      </c>
-      <c r="C41" s="32">
-        <f t="shared" si="0"/>
-        <v>4.1515981735159819</v>
-      </c>
-      <c r="D41" s="32">
-        <f t="shared" si="1"/>
-        <v>4151.5981735159821</v>
-      </c>
-      <c r="I41" s="32"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="B42" s="32">
-        <v>8368</v>
-      </c>
-      <c r="C42" s="32">
-        <f t="shared" si="0"/>
-        <v>1.9105022831050229</v>
-      </c>
-      <c r="D42" s="32">
-        <f t="shared" si="1"/>
-        <v>1910.5022831050228</v>
-      </c>
-      <c r="I42" s="32"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="45" t="s">
-        <v>177</v>
-      </c>
-      <c r="B43" s="32">
-        <v>59</v>
-      </c>
-      <c r="C43" s="32">
-        <f t="shared" si="0"/>
-        <v>1.3470319634703196E-2</v>
-      </c>
-      <c r="D43" s="32">
-        <f t="shared" si="1"/>
-        <v>13.470319634703197</v>
-      </c>
-      <c r="I43" s="32"/>
-    </row>
-    <row r="44" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="B44" s="32">
-        <v>1889</v>
-      </c>
-      <c r="C44" s="32">
-        <f t="shared" si="0"/>
-        <v>0.43127853881278538</v>
-      </c>
-      <c r="D44" s="32">
-        <f t="shared" si="1"/>
-        <v>431.27853881278537</v>
-      </c>
-      <c r="I44" s="32"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="45" t="s">
-        <v>181</v>
-      </c>
-      <c r="B45" s="32">
-        <v>1047</v>
-      </c>
-      <c r="C45" s="32">
-        <f t="shared" si="0"/>
-        <v>0.23904109589041095</v>
-      </c>
-      <c r="D45" s="32">
-        <f t="shared" si="1"/>
-        <v>239.04109589041096</v>
-      </c>
-      <c r="I45" s="32"/>
-    </row>
-    <row r="46" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="45" t="s">
-        <v>183</v>
-      </c>
-      <c r="B46" s="32">
-        <v>5745</v>
-      </c>
-      <c r="C46" s="32">
-        <f t="shared" si="0"/>
-        <v>1.3116438356164384</v>
-      </c>
-      <c r="D46" s="32">
-        <f t="shared" si="1"/>
-        <v>1311.6438356164383</v>
-      </c>
-      <c r="I46" s="32"/>
-    </row>
-    <row r="47" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="B47" s="32">
-        <v>3006</v>
-      </c>
-      <c r="C47" s="32">
-        <f t="shared" si="0"/>
-        <v>0.68630136986301371</v>
-      </c>
-      <c r="D47" s="32">
-        <f t="shared" si="1"/>
-        <v>686.30136986301375</v>
-      </c>
-      <c r="I47" s="32"/>
-    </row>
-    <row r="48" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="45" t="s">
-        <v>187</v>
-      </c>
-      <c r="B48" s="32">
-        <v>3528</v>
-      </c>
-      <c r="C48" s="32">
-        <f t="shared" si="0"/>
-        <v>0.80547945205479454</v>
-      </c>
-      <c r="D48" s="32">
-        <f t="shared" si="1"/>
-        <v>805.47945205479459</v>
-      </c>
-      <c r="I48" s="32"/>
-    </row>
-    <row r="49" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="45" t="s">
-        <v>189</v>
-      </c>
-      <c r="B49" s="32">
-        <v>1710</v>
-      </c>
-      <c r="C49" s="32">
-        <f t="shared" si="0"/>
-        <v>0.3904109589041096</v>
-      </c>
-      <c r="D49" s="32">
-        <f t="shared" si="1"/>
-        <v>390.41095890410958</v>
-      </c>
-      <c r="I49" s="32"/>
-    </row>
-    <row r="50" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="45" t="s">
-        <v>191</v>
-      </c>
-      <c r="B50" s="32">
-        <v>3657</v>
-      </c>
-      <c r="C50" s="32">
-        <f t="shared" si="0"/>
-        <v>0.83493150684931505</v>
-      </c>
-      <c r="D50" s="32">
-        <f t="shared" si="1"/>
-        <v>834.93150684931504</v>
-      </c>
-      <c r="I50" s="32"/>
-    </row>
-    <row r="51" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="45" t="s">
-        <v>193</v>
-      </c>
-      <c r="B51" s="32">
-        <v>27249</v>
-      </c>
-      <c r="C51" s="32">
-        <f t="shared" si="0"/>
-        <v>6.2212328767123291</v>
-      </c>
-      <c r="D51" s="32">
-        <f t="shared" si="1"/>
-        <v>6221.232876712329</v>
-      </c>
-      <c r="I51" s="32"/>
-    </row>
-    <row r="52" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="45" t="s">
-        <v>195</v>
-      </c>
-      <c r="B52" s="32">
-        <v>4408</v>
-      </c>
-      <c r="C52" s="32">
-        <f t="shared" si="0"/>
-        <v>1.006392694063927</v>
-      </c>
-      <c r="D52" s="32">
-        <f t="shared" si="1"/>
-        <v>1006.3926940639269</v>
-      </c>
-      <c r="I52" s="60"/>
-    </row>
-    <row r="53" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="45" t="s">
-        <v>197</v>
-      </c>
-      <c r="B53" s="32">
-        <v>2287</v>
-      </c>
-      <c r="C53" s="32">
-        <f t="shared" si="0"/>
-        <v>0.52214611872146122</v>
-      </c>
-      <c r="D53" s="32">
-        <f t="shared" si="1"/>
-        <v>522.14611872146122</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="45" t="s">
-        <v>199</v>
-      </c>
-      <c r="B54" s="32">
-        <v>4445</v>
-      </c>
-      <c r="C54" s="32">
-        <f t="shared" si="0"/>
-        <v>1.0148401826484019</v>
-      </c>
-      <c r="D54" s="32">
-        <f t="shared" si="1"/>
-        <v>1014.8401826484019</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="50"/>
-    </row>
-    <row r="56" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I58" s="65"/>
-      <c r="J58" s="65"/>
-      <c r="K58" s="65"/>
-      <c r="L58" s="65"/>
-      <c r="M58" s="65"/>
-    </row>
-    <row r="59" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I59" s="66"/>
-      <c r="J59" s="67"/>
-      <c r="K59" s="68"/>
-      <c r="L59" s="68"/>
-      <c r="M59" s="69"/>
-    </row>
-    <row r="60" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I60" s="67"/>
-      <c r="J60" s="68"/>
-      <c r="K60" s="68"/>
-      <c r="L60" s="69"/>
-    </row>
-    <row r="61" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I61" s="66"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="68"/>
-      <c r="L61" s="68"/>
-      <c r="M61" s="69"/>
-    </row>
-    <row r="62" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="B62" s="58" t="s">
-        <v>233</v>
-      </c>
-      <c r="I62" s="67"/>
-      <c r="J62" s="68"/>
-      <c r="K62" s="68"/>
-      <c r="L62" s="69"/>
-    </row>
-    <row r="63" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="50" t="s">
-        <v>234</v>
-      </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="H63" s="61" t="s">
-        <v>235</v>
-      </c>
-      <c r="I63" s="51" t="s">
-        <v>236</v>
-      </c>
-      <c r="J63" s="67"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="68"/>
-      <c r="M63" s="69"/>
-    </row>
-    <row r="64" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="45" t="s">
-        <v>237</v>
-      </c>
-      <c r="B64" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="C64" s="45" t="s">
-        <v>239</v>
-      </c>
-      <c r="D64" s="45" t="s">
-        <v>240</v>
-      </c>
-      <c r="E64" s="45" t="s">
-        <v>241</v>
-      </c>
-      <c r="F64" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="G64" s="32" t="s">
-        <v>101</v>
-      </c>
-      <c r="J64" s="68"/>
-      <c r="K64" s="68"/>
-      <c r="L64" s="69"/>
-    </row>
-    <row r="65" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="45" t="s">
-        <v>243</v>
-      </c>
-      <c r="B65" s="45">
-        <f>1050+1093</f>
-        <v>2143</v>
-      </c>
-      <c r="C65" s="45">
-        <f>6161000 + 6272000</f>
-        <v>12433000</v>
-      </c>
-      <c r="D65" s="70">
-        <v>0.67</v>
-      </c>
-      <c r="E65" s="45" t="s">
-        <v>244</v>
-      </c>
-      <c r="F65" s="32">
-        <f>B65/5</f>
-        <v>428.6</v>
-      </c>
-      <c r="G65" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="J65" s="67"/>
-      <c r="K65" s="67"/>
-      <c r="L65" s="68"/>
-      <c r="M65" s="69"/>
-    </row>
-    <row r="66" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="B66" s="45">
-        <f>3043+1667</f>
-        <v>4710</v>
-      </c>
-      <c r="C66" s="45">
-        <f>16711000+9234000</f>
-        <v>25945000</v>
-      </c>
-      <c r="D66" s="70">
-        <v>0.63</v>
-      </c>
-      <c r="E66" s="45" t="s">
-        <v>246</v>
-      </c>
-      <c r="F66" s="32">
-        <f>B66/7</f>
-        <v>672.85714285714289</v>
-      </c>
-      <c r="G66" s="71" t="s">
-        <v>105</v>
-      </c>
-      <c r="H66" s="32">
-        <f>F77+F78</f>
-        <v>1477.6</v>
-      </c>
-      <c r="I66" s="32" t="s">
-        <v>247</v>
-      </c>
-      <c r="J66" s="68"/>
-      <c r="K66" s="68"/>
-      <c r="L66" s="69"/>
-    </row>
-    <row r="67" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="B67" s="45">
-        <f>1389+1172</f>
-        <v>2561</v>
-      </c>
-      <c r="C67" s="45">
-        <f>7785000+6420000</f>
-        <v>14205000</v>
-      </c>
-      <c r="D67" s="70">
-        <v>0.64</v>
-      </c>
-      <c r="E67" s="45" t="s">
-        <v>249</v>
-      </c>
-      <c r="F67" s="32">
-        <f>B67/6</f>
-        <v>426.83333333333331</v>
-      </c>
-      <c r="G67" s="32" t="s">
-        <v>107</v>
-      </c>
-      <c r="J67" s="67"/>
-      <c r="K67" s="68"/>
-      <c r="L67" s="68"/>
-      <c r="M67" s="69"/>
-    </row>
-    <row r="68" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="B68" s="45">
-        <f>1160+265</f>
-        <v>1425</v>
-      </c>
-      <c r="C68" s="45">
-        <f>1538000+6906000</f>
-        <v>8444000</v>
-      </c>
-      <c r="D68" s="70">
-        <v>0.68</v>
-      </c>
-      <c r="E68" s="45" t="s">
-        <v>251</v>
-      </c>
-      <c r="F68" s="32">
-        <f>B68/4</f>
-        <v>356.25</v>
-      </c>
-      <c r="G68" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="J68" s="68"/>
-      <c r="K68" s="68"/>
-      <c r="L68" s="69"/>
-    </row>
-    <row r="69" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="45" t="s">
-        <v>168</v>
-      </c>
-      <c r="B69" s="45">
-        <v>4757</v>
-      </c>
-      <c r="C69" s="45"/>
-      <c r="D69" s="70">
-        <v>0.61</v>
-      </c>
-      <c r="E69" s="45" t="s">
-        <v>252</v>
-      </c>
-      <c r="F69" s="32">
-        <f>B69/6</f>
-        <v>792.83333333333337</v>
-      </c>
-      <c r="G69" s="71" t="s">
-        <v>111</v>
-      </c>
-      <c r="H69" s="32">
-        <f>F78</f>
-        <v>871</v>
-      </c>
-      <c r="I69" s="32" t="s">
-        <v>253</v>
-      </c>
-      <c r="J69" s="67"/>
-      <c r="K69" s="67"/>
-      <c r="L69" s="68"/>
-      <c r="M69" s="69"/>
-    </row>
-    <row r="70" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="45" t="s">
-        <v>182</v>
-      </c>
-      <c r="B70" s="45">
-        <v>1363</v>
-      </c>
-      <c r="C70" s="45"/>
-      <c r="D70" s="70">
-        <v>0.67</v>
-      </c>
-      <c r="E70" s="45" t="s">
-        <v>254</v>
-      </c>
-      <c r="F70" s="32">
-        <f>B70/2</f>
-        <v>681.5</v>
-      </c>
-      <c r="G70" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="H70" s="32">
-        <f>F66</f>
-        <v>672.85714285714289</v>
-      </c>
-      <c r="I70" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="J70" s="67"/>
-      <c r="K70" s="68"/>
-      <c r="L70" s="69"/>
-    </row>
-    <row r="71" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="B71" s="45">
-        <v>2081</v>
-      </c>
-      <c r="C71" s="45"/>
-      <c r="D71" s="70">
-        <v>0.65</v>
-      </c>
-      <c r="E71" s="45" t="s">
-        <v>256</v>
-      </c>
-      <c r="F71" s="32">
-        <f>B71/5</f>
-        <v>416.2</v>
-      </c>
-      <c r="G71" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="H71" s="32">
-        <f>F66</f>
-        <v>672.85714285714289</v>
-      </c>
-      <c r="I71" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="J71" s="67"/>
-      <c r="K71" s="68"/>
-      <c r="L71" s="68"/>
-      <c r="M71" s="69"/>
-    </row>
-    <row r="72" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="45" t="s">
-        <v>257</v>
-      </c>
-      <c r="B72" s="45">
-        <f>1741+331</f>
-        <v>2072</v>
-      </c>
-      <c r="C72" s="45"/>
-      <c r="D72" s="70">
-        <v>0.68</v>
-      </c>
-      <c r="E72" s="45" t="s">
-        <v>258</v>
-      </c>
-      <c r="F72" s="32">
-        <f>B72/3</f>
-        <v>690.66666666666663</v>
-      </c>
-      <c r="G72" s="71" t="s">
-        <v>117</v>
-      </c>
-      <c r="H72" s="32">
-        <f>M126</f>
-        <v>0</v>
-      </c>
-      <c r="I72" s="45" t="s">
-        <v>248</v>
-      </c>
-      <c r="J72" s="68"/>
-      <c r="K72" s="68"/>
-      <c r="L72" s="69"/>
-    </row>
-    <row r="73" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
-        <v>259</v>
-      </c>
-      <c r="B73" s="45">
-        <f>68+82</f>
-        <v>150</v>
-      </c>
-      <c r="C73" s="45"/>
-      <c r="D73" s="70">
-        <v>0.63</v>
-      </c>
-      <c r="E73" s="45" t="s">
-        <v>260</v>
-      </c>
-      <c r="F73" s="32">
-        <f>B73/2</f>
-        <v>75</v>
-      </c>
-      <c r="G73" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="J73" s="67"/>
-      <c r="K73" s="68"/>
-      <c r="L73" s="68"/>
-      <c r="M73" s="69"/>
-    </row>
-    <row r="74" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="45" t="s">
-        <v>148</v>
-      </c>
-      <c r="B74" s="45">
-        <f>3027+8659</f>
-        <v>11686</v>
-      </c>
-      <c r="C74" s="45"/>
-      <c r="D74" s="70">
-        <v>0.68</v>
-      </c>
-      <c r="E74" s="45" t="s">
-        <v>261</v>
-      </c>
-      <c r="F74" s="32">
-        <f>B74/7</f>
-        <v>1669.4285714285713</v>
-      </c>
-      <c r="G74" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="J74" s="67"/>
-      <c r="K74" s="68"/>
-      <c r="L74" s="69"/>
-    </row>
-    <row r="75" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="45" t="s">
-        <v>262</v>
-      </c>
-      <c r="B75" s="45">
-        <f>395+388</f>
-        <v>783</v>
-      </c>
-      <c r="C75" s="45"/>
-      <c r="D75" s="70">
-        <v>0.66</v>
-      </c>
-      <c r="E75" s="45" t="s">
-        <v>185</v>
-      </c>
-      <c r="F75" s="32">
-        <f>B75</f>
-        <v>783</v>
-      </c>
-      <c r="G75" s="32" t="s">
-        <v>123</v>
-      </c>
-      <c r="J75" s="67"/>
-      <c r="K75" s="67"/>
-      <c r="L75" s="68"/>
-      <c r="M75" s="69"/>
-    </row>
-    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="45" t="s">
-        <v>263</v>
-      </c>
-      <c r="B76" s="45">
-        <f>1336+301</f>
-        <v>1637</v>
-      </c>
-      <c r="C76" s="45"/>
-      <c r="D76" s="70">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E76" s="45" t="s">
-        <v>264</v>
-      </c>
-      <c r="F76" s="32">
-        <f>B76/2</f>
-        <v>818.5</v>
-      </c>
-      <c r="G76" s="71" t="s">
-        <v>125</v>
-      </c>
-      <c r="H76" s="32">
-        <f>F71</f>
-        <v>416.2</v>
-      </c>
-      <c r="I76" s="45" t="s">
-        <v>255</v>
-      </c>
-      <c r="J76" s="67"/>
-      <c r="K76" s="68"/>
-      <c r="L76" s="69"/>
-    </row>
-    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="45" t="s">
-        <v>265</v>
-      </c>
-      <c r="B77" s="45">
-        <f>1942+1091</f>
-        <v>3033</v>
-      </c>
-      <c r="C77" s="45"/>
-      <c r="D77" s="70">
-        <v>0.66</v>
-      </c>
-      <c r="E77" s="45" t="s">
-        <v>266</v>
-      </c>
-      <c r="F77" s="32">
-        <f>B77/5</f>
-        <v>606.6</v>
-      </c>
-      <c r="G77" s="71" t="s">
-        <v>127</v>
-      </c>
-      <c r="H77" s="63">
-        <v>792.83333330000005</v>
-      </c>
-      <c r="I77" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="J77" s="67"/>
-      <c r="K77" s="68"/>
-      <c r="L77" s="68"/>
-      <c r="M77" s="69"/>
-    </row>
-    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="45" t="s">
-        <v>253</v>
-      </c>
-      <c r="B78" s="45">
-        <f>2166+447</f>
-        <v>2613</v>
-      </c>
-      <c r="C78" s="45"/>
-      <c r="D78" s="70">
-        <v>0.7</v>
-      </c>
-      <c r="E78" s="45" t="s">
-        <v>267</v>
-      </c>
-      <c r="F78" s="32">
-        <f t="shared" ref="F78:F79" si="2">B78/3</f>
-        <v>871</v>
-      </c>
-      <c r="G78" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="J78" s="68"/>
-      <c r="K78" s="68"/>
-      <c r="L78" s="69"/>
-    </row>
-    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="B79" s="45">
-        <f>148+416</f>
-        <v>564</v>
-      </c>
-      <c r="C79" s="45"/>
-      <c r="D79" s="70">
-        <v>0.65</v>
-      </c>
-      <c r="E79" s="45" t="s">
-        <v>269</v>
-      </c>
-      <c r="F79" s="32">
-        <f t="shared" si="2"/>
-        <v>188</v>
-      </c>
-      <c r="G79" s="32" t="s">
-        <v>131</v>
-      </c>
-      <c r="J79" s="67"/>
-      <c r="K79" s="68"/>
-      <c r="L79" s="68"/>
-      <c r="M79" s="69"/>
-    </row>
-    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="45" t="s">
-        <v>270</v>
-      </c>
-      <c r="B80" s="45">
-        <f>15997+9228</f>
-        <v>25225</v>
-      </c>
-      <c r="C80" s="45"/>
-      <c r="D80" s="70">
-        <v>0.69</v>
-      </c>
-      <c r="E80" s="45" t="s">
-        <v>271</v>
-      </c>
-      <c r="F80" s="32">
-        <f>B80/4</f>
-        <v>6306.25</v>
-      </c>
-      <c r="G80" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="J80" s="68"/>
-      <c r="K80" s="68"/>
-      <c r="L80" s="69"/>
-    </row>
-    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="B81" s="45">
-        <f>4029+3025</f>
-        <v>7054</v>
-      </c>
-      <c r="C81" s="45"/>
-      <c r="D81" s="70">
-        <v>0.63</v>
-      </c>
-      <c r="E81" s="72" t="s">
-        <v>110</v>
-      </c>
-      <c r="F81" s="32">
-        <f t="shared" ref="F81:F83" si="3">B81</f>
-        <v>7054</v>
-      </c>
-      <c r="G81" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="J81" s="67"/>
-      <c r="K81" s="67"/>
-      <c r="L81" s="68"/>
-      <c r="M81" s="69"/>
-    </row>
-    <row r="82" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="B82" s="45">
-        <v>4723</v>
-      </c>
-      <c r="C82" s="45"/>
-      <c r="D82" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="E82" s="45"/>
-      <c r="F82" s="32">
-        <f t="shared" si="3"/>
-        <v>4723</v>
-      </c>
-      <c r="G82" s="71" t="s">
-        <v>137</v>
-      </c>
-      <c r="H82" s="32">
-        <f t="shared" ref="H82:H83" si="4">F65</f>
-        <v>428.6</v>
-      </c>
-      <c r="I82" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="J82" s="67"/>
-      <c r="K82" s="68"/>
-      <c r="L82" s="69"/>
-    </row>
-    <row r="83" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="B83" s="45">
-        <v>145</v>
-      </c>
-      <c r="C83" s="45"/>
-      <c r="D83" s="70">
-        <v>0.53</v>
-      </c>
-      <c r="E83" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="F83" s="32">
-        <f t="shared" si="3"/>
-        <v>145</v>
-      </c>
-      <c r="G83" s="71" t="s">
-        <v>139</v>
-      </c>
-      <c r="H83" s="32">
-        <f t="shared" si="4"/>
-        <v>672.85714285714289</v>
-      </c>
-      <c r="I83" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="J83" s="67"/>
-      <c r="K83" s="68"/>
-      <c r="L83" s="68"/>
-      <c r="M83" s="69"/>
-    </row>
-    <row r="84" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G84" s="32" t="s">
-        <v>141</v>
-      </c>
-      <c r="I84" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="J84" s="67"/>
-      <c r="K84" s="68"/>
-      <c r="L84" s="69"/>
-    </row>
-    <row r="85" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G85" s="71" t="s">
-        <v>143</v>
-      </c>
-      <c r="H85" s="63">
-        <f>F68</f>
-        <v>356.25</v>
-      </c>
-      <c r="I85" s="45" t="s">
-        <v>250</v>
-      </c>
-      <c r="J85" s="67"/>
-      <c r="K85" s="68"/>
-      <c r="L85" s="68"/>
-      <c r="M85" s="69"/>
-    </row>
-    <row r="86" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G86" s="71" t="s">
-        <v>99</v>
-      </c>
-      <c r="H86" s="45">
-        <f>F73+F71</f>
-        <v>491.2</v>
-      </c>
-      <c r="I86" s="32" t="s">
-        <v>272</v>
-      </c>
-      <c r="J86" s="68"/>
-      <c r="K86" s="68"/>
-      <c r="L86" s="69"/>
-    </row>
-    <row r="87" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G87" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="J87" s="67"/>
-      <c r="K87" s="68"/>
-      <c r="L87" s="68"/>
-      <c r="M87" s="69"/>
-    </row>
-    <row r="88" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G88" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="J88" s="67"/>
-      <c r="K88" s="68"/>
-      <c r="L88" s="69"/>
-    </row>
-    <row r="89" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G89" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="J89" s="67"/>
-      <c r="K89" s="67"/>
-      <c r="L89" s="68"/>
-      <c r="M89" s="69"/>
-    </row>
-    <row r="90" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G90" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="J90" s="67"/>
-      <c r="K90" s="68"/>
-      <c r="L90" s="69"/>
-    </row>
-    <row r="91" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G91" s="71" t="s">
-        <v>154</v>
-      </c>
-      <c r="H91" s="32">
-        <f>F78+F79</f>
-        <v>1059</v>
-      </c>
-      <c r="I91" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="J91" s="67"/>
-      <c r="K91" s="68"/>
-      <c r="L91" s="68"/>
-      <c r="M91" s="69"/>
-    </row>
-    <row r="92" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G92" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="I92" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="J92" s="68"/>
-      <c r="K92" s="68"/>
-      <c r="L92" s="69"/>
-    </row>
-    <row r="93" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G93" s="71" t="s">
-        <v>158</v>
-      </c>
-      <c r="H93" s="32">
-        <f>F66</f>
-        <v>672.85714285714289</v>
-      </c>
-      <c r="I93" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="J93" s="67"/>
-      <c r="K93" s="68"/>
-      <c r="L93" s="68"/>
-      <c r="M93" s="69"/>
-    </row>
-    <row r="94" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G94" s="71" t="s">
-        <v>160</v>
-      </c>
-      <c r="H94" s="32">
-        <f>F78+F79</f>
-        <v>1059</v>
-      </c>
-      <c r="I94" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="J94" s="68"/>
-      <c r="K94" s="68"/>
-      <c r="L94" s="69"/>
-    </row>
-    <row r="95" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G95" s="32" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G96" s="71" t="s">
-        <v>164</v>
-      </c>
-      <c r="H96" s="32">
-        <f>+F67+F70</f>
-        <v>1108.3333333333333</v>
-      </c>
-      <c r="I96" s="45" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="97" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G97" s="32" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="98" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G98" s="71" t="s">
-        <v>168</v>
-      </c>
-      <c r="H98" s="32">
-        <f>F68+F69</f>
-        <v>1149.0833333333335</v>
-      </c>
-      <c r="I98" s="32" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="99" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G99" s="32" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="100" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G100" s="71" t="s">
-        <v>172</v>
-      </c>
-      <c r="H100" s="64">
-        <f>F80</f>
-        <v>6306.25</v>
-      </c>
-      <c r="I100" s="45" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="101" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G101" s="71" t="s">
-        <v>174</v>
-      </c>
-      <c r="H101" s="32">
-        <f>F66+F69</f>
-        <v>1465.6904761904761</v>
-      </c>
-      <c r="I101" s="32" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="102" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G102" s="32" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="103" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G103" s="32" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="104" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G104" s="32" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="105" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G105" s="32" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="106" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G106" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="H106" s="32">
-        <f>F75+F76</f>
-        <v>1601.5</v>
-      </c>
-      <c r="I106" s="73" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="107" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G107" s="32" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="108" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G108" s="32" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="109" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G109" s="71" t="s">
-        <v>190</v>
-      </c>
-      <c r="H109" s="32">
-        <f>F66+F69</f>
-        <v>1465.6904761904761</v>
-      </c>
-      <c r="I109" s="32" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="110" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G110" s="32" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="111" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G111" s="32" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="112" spans="7:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G112" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="H112" s="32">
-        <f>F68+F71</f>
-        <v>772.45</v>
-      </c>
-      <c r="I112" s="32" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="113" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G113" s="60" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="114" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" spans="7:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B62" r:id="rId1" xr:uid="{31584BB2-B7E7-4133-B487-37CDDD4F8072}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-</worksheet>
 </file>
--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\WI\elec\MPCbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB724114-E04C-49AB-87E3-18B8CB2CEC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6A77F44-B5E5-446B-B600-24DE1655CC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="195" windowWidth="20805" windowHeight="9765" firstSheet="6" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="1575" windowWidth="15870" windowHeight="16425" firstSheet="7" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
     <sheet name="Data" sheetId="2" r:id="rId11"/>
     <sheet name="MPCbS" sheetId="3" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="1.0000000000000001E-5"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1715,7 +1715,7 @@
         <v>196</v>
       </c>
       <c r="C1" s="24">
-        <v>45301</v>
+        <v>45348</v>
       </c>
       <c r="H1" s="25" t="s">
         <v>100</v>
@@ -5633,8 +5633,7 @@
         <v>57</v>
       </c>
       <c r="B16" s="14">
-        <f>B12</f>
-        <v>9000000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -5660,7 +5659,7 @@
         <v>92</v>
       </c>
       <c r="B19" s="14">
-        <f>9*10^12</f>
+        <f>B2</f>
         <v>9000000000000</v>
       </c>
     </row>
@@ -5687,7 +5686,7 @@
         <v>95</v>
       </c>
       <c r="B22" s="14">
-        <f>IF(INDEX('coal ban'!D:D,MATCH(About!$B$2,'coal ban'!C:C,0))="yes",0,9*10^12)</f>
+        <f>B2</f>
         <v>9000000000000</v>
       </c>
     </row>
@@ -5946,7 +5945,7 @@
         <v>138</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
@@ -6144,7 +6143,7 @@
         <v>173</v>
       </c>
       <c r="D38" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
